--- a/rich_v2_autotest/迭代三测试资料包/迭代三自动化测试_ERROR_FAIL原因汇总.xlsx
+++ b/rich_v2_autotest/迭代三测试资料包/迭代三自动化测试_ERROR_FAIL原因汇总.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdf11b41ece2c4465"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题明细" sheetId="2" r:id="Rce2b9436109f457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERROR明细" sheetId="3" r:id="Ra00df7b6d603412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAIL明细" sheetId="4" r:id="Rd2b3910304a04519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R04ece01e64834366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题明细" sheetId="2" r:id="Rd0043d58d1204a70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERROR明细" sheetId="3" r:id="Rf7ea964fdf57475e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAIL明细" sheetId="4" r:id="R50f6ce33498a4e00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -444,8 +444,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllIssuesTable" displayName="AllIssuesTable" ref="A4:J57" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:J57"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllIssuesTable" displayName="AllIssuesTable" ref="A4:J52" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J52"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="用例ID"/>
@@ -463,8 +463,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ErrorsTable" displayName="ErrorsTable" ref="A4:J39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:J39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ErrorsTable" displayName="ErrorsTable" ref="A4:J38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J38"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="用例ID"/>
@@ -482,8 +482,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FailsTable" displayName="FailsTable" ref="A4:J22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:J22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FailsTable" displayName="FailsTable" ref="A4:J18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J18"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="用例ID"/>
@@ -715,7 +715,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>依据：results_state_v2.json 与 results_interactive_v2.json；统计对象为最新版288条正向用例的一键回归结果</x:v>
+        <x:v>依据：修复6条测试资产问题后重新生成的 results_state_v2.json 与 results_interactive_v2.json；统计对象为最新版288条正向用例</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -748,13 +748,13 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B5" s="26" t="n">
-        <x:v>205</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C5" s="26" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D5" s="26" t="n">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="26" t="n">
         <x:v>30</x:v>
@@ -785,28 +785,28 @@
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
       <x:c r="A8" s="36" t="n">
-        <x:f>COUNTA('问题明细'!$B$5:$B$57)</x:f>
-        <x:v>53</x:v>
+        <x:f>COUNTA('问题明细'!$B$5:$B$52)</x:f>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="37" t="n">
-        <x:f>COUNTIF('问题明细'!$C$5:$C$57,"ERROR")</x:f>
-        <x:v>35</x:v>
+        <x:f>COUNTIF('问题明细'!$C$5:$C$52,"ERROR")</x:f>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="37" t="n">
-        <x:f>COUNTIF('问题明细'!$C$5:$C$57,"FAIL")</x:f>
-        <x:v>18</x:v>
+        <x:f>COUNTIF('问题明细'!$C$5:$C$52,"FAIL")</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="37" t="n">
-        <x:f>COUNTIF('问题明细'!$H$5:$H$57,"开发/测试接口适配")</x:f>
+        <x:f>COUNTIF('问题明细'!$H$5:$H$52,"开发/测试接口适配")</x:f>
         <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="37" t="n">
-        <x:f>COUNTIF('问题明细'!$H$5:$H$57,"测试资产")</x:f>
+        <x:f>COUNTIF('问题明细'!$H$5:$H$52,"测试资产")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="38" t="n">
+        <x:f>COUNTIF('问题明细'!$H$5:$H$52,"开发逻辑/测试接口")+COUNTIF('问题明细'!$H$5:$H$52,"开发逻辑")+COUNTIF('问题明细'!$H$5:$H$52,"开发逻辑/地图事件接入")</x:f>
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="F8" s="38" t="n">
-        <x:f>COUNTIF('问题明细'!$H$5:$H$57,"开发逻辑/测试接口")+COUNTIF('问题明细'!$H$5:$H$57,"开发逻辑")+COUNTIF('问题明细'!$H$5:$H$57,"开发逻辑/地图事件接入")</x:f>
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -834,12 +834,12 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="B11" s="52" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A11)</x:f>
+        <x:f>COUNTIF('问题明细'!$F$5:$F$52,A11)</x:f>
         <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="58" t="n">
         <x:f>B11/$A$8</x:f>
-        <x:v>0.4339622641509434</x:v>
+        <x:v>0.4791666666666667</x:v>
       </x:c>
       <x:c r="D11" s="46" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -856,12 +856,12 @@
         <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
       <x:c r="B12" s="53" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A12)</x:f>
+        <x:f>COUNTIF('问题明细'!$F$5:$F$52,A12)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="59" t="n">
         <x:f>B12/$A$8</x:f>
-        <x:v>0.20754716981132076</x:v>
+        <x:v>0.22916666666666666</x:v>
       </x:c>
       <x:c r="D12" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -878,12 +878,12 @@
         <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="B13" s="53" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A13)</x:f>
+        <x:f>COUNTIF('问题明细'!$F$5:$F$52,A13)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="59" t="n">
         <x:f>B13/$A$8</x:f>
-        <x:v>0.1509433962264151</x:v>
+        <x:v>0.16666666666666666</x:v>
       </x:c>
       <x:c r="D13" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -897,117 +897,73 @@
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="47" t="str">
-        <x:v>测试步骤未处理落点提示</x:v>
+        <x:v>财神领取与免租未接入</x:v>
       </x:c>
       <x:c r="B14" s="53" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A14)</x:f>
-        <x:v>2</x:v>
+        <x:f>COUNTIF('问题明细'!$F$5:$F$52,A14)</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C14" s="59" t="n">
         <x:f>B14/$A$8</x:f>
-        <x:v>0.03773584905660377</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="D14" s="47" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发逻辑/测试接口</x:v>
       </x:c>
       <x:c r="E14" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F14" s="47" t="str">
-        <x:v>补充ANSWER或调整不触发提示的落点</x:v>
+        <x:v>实现领取、移除F和当轮免租</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
+        <x:v>礼品屋财神奖励未实现</x:v>
       </x:c>
       <x:c r="B15" s="53" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A15)</x:f>
-        <x:v>4</x:v>
+        <x:f>COUNTIF('问题明细'!$F$5:$F$52,A15)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="59" t="n">
         <x:f>B15/$A$8</x:f>
-        <x:v>0.07547169811320754</x:v>
+        <x:v>0.020833333333333332</x:v>
       </x:c>
       <x:c r="D15" s="47" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发逻辑</x:v>
       </x:c>
       <x:c r="E15" s="62" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F15" s="47" t="str">
-        <x:v>依据原Excel修复四条资金期望</x:v>
+        <x:v>实现礼品3授予5回合财神</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
-      <x:c r="A16" s="47" t="str">
-        <x:v>财神领取与免租未接入</x:v>
-      </x:c>
-      <x:c r="B16" s="53" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A16)</x:f>
+      <x:c r="A16" s="48" t="str">
+        <x:v>道具屋落点未触发PROMPT</x:v>
+      </x:c>
+      <x:c r="B16" s="54" t="n">
+        <x:f>COUNTIF('问题明细'!$F$5:$F$52,A16)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C16" s="59" t="n">
+      <x:c r="C16" s="60" t="n">
         <x:f>B16/$A$8</x:f>
-        <x:v>0.03773584905660377</x:v>
-      </x:c>
-      <x:c r="D16" s="47" t="str">
-        <x:v>开发逻辑/测试接口</x:v>
-      </x:c>
-      <x:c r="E16" s="62" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="F16" s="47" t="str">
-        <x:v>实现领取、移除F和当轮免租</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="42" customHeight="1">
-      <x:c r="A17" s="47" t="str">
-        <x:v>礼品屋财神奖励未实现</x:v>
-      </x:c>
-      <x:c r="B17" s="53" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="59" t="n">
-        <x:f>B17/$A$8</x:f>
-        <x:v>0.018867924528301886</x:v>
-      </x:c>
-      <x:c r="D17" s="47" t="str">
-        <x:v>开发逻辑</x:v>
-      </x:c>
-      <x:c r="E17" s="62" t="str">
+        <x:v>0.041666666666666664</x:v>
+      </x:c>
+      <x:c r="D16" s="48" t="str">
+        <x:v>开发逻辑/地图事件接入</x:v>
+      </x:c>
+      <x:c r="E16" s="63" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="F17" s="47" t="str">
-        <x:v>实现礼品3授予5回合财神</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="42" customHeight="1">
-      <x:c r="A18" s="48" t="str">
-        <x:v>道具屋落点未触发PROMPT</x:v>
-      </x:c>
-      <x:c r="B18" s="54" t="n">
-        <x:f>COUNTIF('问题明细'!$F$5:$F$57,A18)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="60" t="n">
-        <x:f>B18/$A$8</x:f>
-        <x:v>0.03773584905660377</x:v>
-      </x:c>
-      <x:c r="D18" s="48" t="str">
-        <x:v>开发逻辑/地图事件接入</x:v>
-      </x:c>
-      <x:c r="E18" s="63" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="F18" s="48" t="str">
+      <x:c r="F16" s="48" t="str">
         <x:v>接入位置28道具屋提示</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="68" t="str">
-        <x:v>结论：ERROR主要是2.0测试控制接口未接入，不代表业务断言失败；FAIL中同时存在开发缺口和6条测试资产问题，应分开处理。</x:v>
+        <x:v>结论：已修复的6条测试资产问题全部通过或转为真实业务断言；当前34条ERROR均为2.0测试控制接口未接入，14条FAIL均指向开发输出或业务逻辑缺口，未再发现测试资产归因。</x:v>
       </x:c>
       <x:c r="B20" s="69"/>
       <x:c r="C20" s="69"/>
@@ -1046,13 +1002,13 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="D23" s="49" t="n">
-        <x:v>205</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E23" s="49" t="n">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="49" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1117,7 +1073,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>共53条；“责任归属”是基于当前报告和2.0规范的测试侧初步判断，修复后应重新执行一键回归确认。</x:v>
+        <x:v>共48条；“责任归属”是基于当前报告和2.0规范的测试侧初步判断，修复后应重新执行一键回归确认。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -1166,31 +1122,31 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="46" t="str">
-        <x:v>Case_A4_001</x:v>
+        <x:v>Case_A4_010</x:v>
       </x:c>
       <x:c r="C5" s="61" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>ERROR</x:v>
       </x:c>
       <x:c r="D5" s="46" t="str">
         <x:v>A4 回合控制与落点处理</x:v>
       </x:c>
       <x:c r="E5" s="46" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.current_user；scalar not equal；期望="A"；实际="Q"</x:v>
+        <x:v>INVALID_ACTION；DICE_SEQUENCE_EMPTY</x:v>
       </x:c>
       <x:c r="F5" s="46" t="str">
-        <x:v>测试步骤未处理落点提示</x:v>
+        <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G5" s="46" t="str">
-        <x:v>Q从公园49 STEP 1后到达位置50的无主地产，当前回合停留在BUY提示，故current_user仍为Q；用例却直接期望切换到A。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[6], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H5" s="46" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I5" s="61" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J5" s="46" t="str">
-        <x:v>在STEP后补充ANSWER拒绝/购买，再断言切换到A；不能仅修改current_user期望来强行通过。</x:v>
+        <x:v>让STATE测试入口解析 random_control.streams.DICE，并按规范逐次消费；同步统一耗尽错误码并增加接口单元测试。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
@@ -1198,7 +1154,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="47" t="str">
-        <x:v>Case_A4_010</x:v>
+        <x:v>Case_A4_011</x:v>
       </x:c>
       <x:c r="C6" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1230,7 +1186,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="47" t="str">
-        <x:v>Case_A4_011</x:v>
+        <x:v>Case_A4_012</x:v>
       </x:c>
       <x:c r="C7" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1245,7 +1201,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G7" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[6], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[1], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H7" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1262,31 +1218,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="47" t="str">
-        <x:v>Case_A4_012</x:v>
+        <x:v>Case_A5_002</x:v>
       </x:c>
       <x:c r="C8" s="62" t="str">
-        <x:v>ERROR</x:v>
+        <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D8" s="47" t="str">
-        <x:v>A4 回合控制与落点处理</x:v>
+        <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E8" s="47" t="str">
-        <x:v>INVALID_ACTION；DICE_SEQUENCE_EMPTY</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"2","visible_entity":"BASE"}]；实际=null</x:v>
       </x:c>
       <x:c r="F8" s="47" t="str">
-        <x:v>V2随机控制未接入</x:v>
+        <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="G8" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[1], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
       </x:c>
       <x:c r="H8" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I8" s="62" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="J8" s="47" t="str">
-        <x:v>让STATE测试入口解析 random_control.streams.DICE，并按规范逐次消费；同步统一耗尽错误码并增加接口单元测试。</x:v>
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
@@ -1294,7 +1250,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="47" t="str">
-        <x:v>Case_A5_002</x:v>
+        <x:v>Case_A5_003</x:v>
       </x:c>
       <x:c r="C9" s="62" t="str">
         <x:v>FAIL</x:v>
@@ -1303,7 +1259,7 @@
         <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E9" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"2","visible_entity":"BASE"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"0","visible_entity":"BASE"}]；实际=null</x:v>
       </x:c>
       <x:c r="F9" s="47" t="str">
         <x:v>Actual缺少display_cells</x:v>
@@ -1326,7 +1282,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="47" t="str">
-        <x:v>Case_A5_003</x:v>
+        <x:v>Case_A5_004</x:v>
       </x:c>
       <x:c r="C10" s="62" t="str">
         <x:v>FAIL</x:v>
@@ -1335,7 +1291,7 @@
         <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E10" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"0","visible_entity":"BASE"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":30,"visible_symbol":"#","visible_entity":"MAP_ITEM"}]；实际=null</x:v>
       </x:c>
       <x:c r="F10" s="47" t="str">
         <x:v>Actual缺少display_cells</x:v>
@@ -1358,7 +1314,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="47" t="str">
-        <x:v>Case_A5_004</x:v>
+        <x:v>Case_A5_005</x:v>
       </x:c>
       <x:c r="C11" s="62" t="str">
         <x:v>FAIL</x:v>
@@ -1367,7 +1323,7 @@
         <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E11" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":30,"visible_symbol":"#","visible_entity":"MAP_ITEM"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"visible_symbol":"Q","visible_entity":"PLAYER"}]；实际=null</x:v>
       </x:c>
       <x:c r="F11" s="47" t="str">
         <x:v>Actual缺少display_cells</x:v>
@@ -1390,31 +1346,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="47" t="str">
-        <x:v>Case_A5_005</x:v>
+        <x:v>Case_A8_003</x:v>
       </x:c>
       <x:c r="C12" s="62" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>ERROR</x:v>
       </x:c>
       <x:c r="D12" s="47" t="str">
-        <x:v>A5 地图显示</x:v>
+        <x:v>A8 Roll掷骰子移动</x:v>
       </x:c>
       <x:c r="E12" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"visible_symbol":"Q","visible_entity":"PLAYER"}]；实际=null</x:v>
+        <x:v>INVALID_ACTION；DICE_SEQUENCE_EMPTY</x:v>
       </x:c>
       <x:c r="F12" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
+        <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G12" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[3], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H12" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I12" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J12" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+        <x:v>让STATE测试入口解析 random_control.streams.DICE，并按规范逐次消费；同步统一耗尽错误码并增加接口单元测试。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -1422,7 +1378,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="47" t="str">
-        <x:v>Case_A8_003</x:v>
+        <x:v>Case_A8_004</x:v>
       </x:c>
       <x:c r="C13" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1437,7 +1393,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G13" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[3], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[2], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H13" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1454,7 +1410,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="47" t="str">
-        <x:v>Case_A8_004</x:v>
+        <x:v>Case_A8_005</x:v>
       </x:c>
       <x:c r="C14" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1486,7 +1442,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="47" t="str">
-        <x:v>Case_A8_005</x:v>
+        <x:v>Case_A8_006</x:v>
       </x:c>
       <x:c r="C15" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1501,7 +1457,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G15" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[2], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[6], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H15" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1518,7 +1474,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="47" t="str">
-        <x:v>Case_A8_006</x:v>
+        <x:v>Case_A8_007</x:v>
       </x:c>
       <x:c r="C16" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1533,7 +1489,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G16" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[6], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[4], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H16" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1550,7 +1506,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="47" t="str">
-        <x:v>Case_A8_007</x:v>
+        <x:v>Case_A8_008</x:v>
       </x:c>
       <x:c r="C17" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1565,7 +1521,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G17" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[4], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[1], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H17" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1582,7 +1538,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" s="47" t="str">
-        <x:v>Case_A8_008</x:v>
+        <x:v>Case_A8_009</x:v>
       </x:c>
       <x:c r="C18" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1597,7 +1553,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G18" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[1], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[5], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H18" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1614,7 +1570,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" s="47" t="str">
-        <x:v>Case_A8_009</x:v>
+        <x:v>Case_A8_010</x:v>
       </x:c>
       <x:c r="C19" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1629,7 +1585,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G19" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[5], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[4], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H19" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1646,7 +1602,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="47" t="str">
-        <x:v>Case_A8_010</x:v>
+        <x:v>Case_A8_011</x:v>
       </x:c>
       <x:c r="C20" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1678,7 +1634,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="47" t="str">
-        <x:v>Case_A8_011</x:v>
+        <x:v>Case_A8_012</x:v>
       </x:c>
       <x:c r="C21" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1693,7 +1649,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G21" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[4], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[5], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H21" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1710,7 +1666,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="47" t="str">
-        <x:v>Case_A8_012</x:v>
+        <x:v>Case_A8_013</x:v>
       </x:c>
       <x:c r="C22" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1725,7 +1681,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G22" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[5], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[2], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H22" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1742,7 +1698,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" s="47" t="str">
-        <x:v>Case_A8_013</x:v>
+        <x:v>Case_A8_014</x:v>
       </x:c>
       <x:c r="C23" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1757,7 +1713,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G23" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[2], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[3], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H23" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1774,7 +1730,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="47" t="str">
-        <x:v>Case_A8_014</x:v>
+        <x:v>Case_A8_015</x:v>
       </x:c>
       <x:c r="C24" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1789,7 +1745,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G24" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[3], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[2], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H24" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1806,7 +1762,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" s="47" t="str">
-        <x:v>Case_A8_015</x:v>
+        <x:v>Case_A8_016</x:v>
       </x:c>
       <x:c r="C25" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1838,7 +1794,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="47" t="str">
-        <x:v>Case_A8_016</x:v>
+        <x:v>Case_A8_017</x:v>
       </x:c>
       <x:c r="C26" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1853,7 +1809,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G26" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[2], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[3], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H26" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1870,7 +1826,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="47" t="str">
-        <x:v>Case_A8_017</x:v>
+        <x:v>Case_A8_018</x:v>
       </x:c>
       <x:c r="C27" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1885,7 +1841,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G27" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[3], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[1], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H27" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1902,7 +1858,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="47" t="str">
-        <x:v>Case_A8_018</x:v>
+        <x:v>Case_A8_019</x:v>
       </x:c>
       <x:c r="C28" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1917,7 +1873,7 @@
         <x:v>V2随机控制未接入</x:v>
       </x:c>
       <x:c r="G28" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[1], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[6], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
       </x:c>
       <x:c r="H28" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -1934,7 +1890,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="47" t="str">
-        <x:v>Case_A8_019</x:v>
+        <x:v>Case_A8_020</x:v>
       </x:c>
       <x:c r="C29" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1966,7 +1922,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" s="47" t="str">
-        <x:v>Case_A8_020</x:v>
+        <x:v>Case_A8_021</x:v>
       </x:c>
       <x:c r="C30" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -1998,7 +1954,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" s="47" t="str">
-        <x:v>Case_A8_021</x:v>
+        <x:v>Case_A8_022</x:v>
       </x:c>
       <x:c r="C31" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -2030,22 +1986,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" s="47" t="str">
-        <x:v>Case_A8_022</x:v>
+        <x:v>Case_A14_001</x:v>
       </x:c>
       <x:c r="C32" s="62" t="str">
         <x:v>ERROR</x:v>
       </x:c>
       <x:c r="D32" s="47" t="str">
-        <x:v>A8 Roll掷骰子移动</x:v>
+        <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E32" s="47" t="str">
-        <x:v>INVALID_ACTION；DICE_SEQUENCE_EMPTY</x:v>
+        <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
       <x:c r="F32" s="47" t="str">
-        <x:v>V2随机控制未接入</x:v>
+        <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
       <x:c r="G32" s="47" t="str">
-        <x:v>用例已按2.0规范提供 random_control.streams.DICE=[6], 但测试入口仍返回旧式 DICE_SEQUENCE_EMPTY，说明 monopoly_test 尚未读取或传递2.0具名随机流。</x:v>
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
       <x:c r="H32" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
@@ -2054,7 +2010,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="J32" s="47" t="str">
-        <x:v>让STATE测试入口解析 random_control.streams.DICE，并按规范逐次消费；同步统一耗尽错误码并增加接口单元测试。</x:v>
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
@@ -2062,32 +2018,31 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="47" t="str">
-        <x:v>Case_A10_014</x:v>
+        <x:v>Case_A14_002</x:v>
       </x:c>
       <x:c r="C33" s="62" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>ERROR</x:v>
       </x:c>
       <x:c r="D33" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
+        <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E33" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=5000；实际=4000
-ASSERT_NOT_EQUAL；字段=actual.players[id=S].fund；scalar not equal；期望=5000；实际=6000</x:v>
+        <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
       <x:c r="F33" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
+        <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
       <x:c r="G33" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
       <x:c r="H33" s="47" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I33" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J33" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
@@ -2095,32 +2050,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" s="47" t="str">
-        <x:v>Case_A10_015</x:v>
+        <x:v>Case_A14_003</x:v>
       </x:c>
       <x:c r="C34" s="62" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>ERROR</x:v>
       </x:c>
       <x:c r="D34" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
+        <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E34" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=S].fund；scalar not equal；期望=5000；实际=4700
-ASSERT_NOT_EQUAL；字段=actual.players[id=J].fund；scalar not equal；期望=5000；实际=5300</x:v>
+        <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
       <x:c r="F34" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
+        <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
       <x:c r="G34" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
       <x:c r="H34" s="47" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I34" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J34" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
@@ -2128,32 +2082,31 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" s="47" t="str">
-        <x:v>Case_A10_017</x:v>
+        <x:v>Case_A14_004</x:v>
       </x:c>
       <x:c r="C35" s="62" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>ERROR</x:v>
       </x:c>
       <x:c r="D35" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
+        <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E35" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=5000；实际=4250
-ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=5000；实际=5750</x:v>
+        <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
       <x:c r="F35" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
+        <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
       <x:c r="G35" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
       <x:c r="H35" s="47" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I35" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J35" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
@@ -2161,32 +2114,31 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="47" t="str">
-        <x:v>Case_A10_018</x:v>
+        <x:v>Case_A14_005</x:v>
       </x:c>
       <x:c r="C36" s="62" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>ERROR</x:v>
       </x:c>
       <x:c r="D36" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
+        <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E36" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=J].fund；scalar not equal；期望=5000；实际=4400
-ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=5000；实际=5600</x:v>
+        <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
       <x:c r="F36" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
+        <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
       <x:c r="G36" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
       <x:c r="H36" s="47" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I36" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J36" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
@@ -2194,7 +2146,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" s="47" t="str">
-        <x:v>Case_A14_001</x:v>
+        <x:v>Case_A14_006</x:v>
       </x:c>
       <x:c r="C37" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -2226,7 +2178,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" s="47" t="str">
-        <x:v>Case_A14_002</x:v>
+        <x:v>Case_A14_007</x:v>
       </x:c>
       <x:c r="C38" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -2258,7 +2210,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" s="47" t="str">
-        <x:v>Case_A14_003</x:v>
+        <x:v>Case_A14_008</x:v>
       </x:c>
       <x:c r="C39" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -2290,31 +2242,32 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" s="47" t="str">
-        <x:v>Case_A14_004</x:v>
+        <x:v>Case_A14_009</x:v>
       </x:c>
       <x:c r="C40" s="62" t="str">
-        <x:v>ERROR</x:v>
+        <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D40" s="47" t="str">
         <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E40" s="47" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.fortune；field missing in actual；期望={"position":null}；实际=null
+ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0</x:v>
       </x:c>
       <x:c r="F40" s="47" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
+        <x:v>财神领取与免租未接入</x:v>
       </x:c>
       <x:c r="G40" s="47" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
+        <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
       </x:c>
       <x:c r="H40" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
+        <x:v>开发逻辑/测试接口</x:v>
       </x:c>
       <x:c r="I40" s="62" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="J40" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
+        <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
@@ -2322,194 +2275,194 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" s="47" t="str">
-        <x:v>Case_A14_005</x:v>
+        <x:v>Case_A14_010</x:v>
       </x:c>
       <x:c r="C41" s="62" t="str">
-        <x:v>ERROR</x:v>
+        <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D41" s="47" t="str">
         <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E41" s="47" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
-      </x:c>
-      <x:c r="F41" s="47" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
-      </x:c>
-      <x:c r="G41" s="47" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
-      </x:c>
-      <x:c r="H41" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I41" s="62" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J41" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="58" customHeight="1">
-      <x:c r="A42" s="53" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B42" s="47" t="str">
-        <x:v>Case_A14_006</x:v>
-      </x:c>
-      <x:c r="C42" s="62" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="D42" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
-      </x:c>
-      <x:c r="E42" s="47" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
-      </x:c>
-      <x:c r="F42" s="47" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
-      </x:c>
-      <x:c r="G42" s="47" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
-      </x:c>
-      <x:c r="H42" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I42" s="62" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J42" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="58" customHeight="1">
-      <x:c r="A43" s="53" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B43" s="47" t="str">
-        <x:v>Case_A14_007</x:v>
-      </x:c>
-      <x:c r="C43" s="62" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="D43" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
-      </x:c>
-      <x:c r="E43" s="47" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
-      </x:c>
-      <x:c r="F43" s="47" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
-      </x:c>
-      <x:c r="G43" s="47" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
-      </x:c>
-      <x:c r="H43" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I43" s="62" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J43" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="58" customHeight="1">
-      <x:c r="A44" s="53" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B44" s="47" t="str">
-        <x:v>Case_A14_008</x:v>
-      </x:c>
-      <x:c r="C44" s="62" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="D44" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
-      </x:c>
-      <x:c r="E44" s="47" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
-      </x:c>
-      <x:c r="F44" s="47" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
-      </x:c>
-      <x:c r="G44" s="47" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
-      </x:c>
-      <x:c r="H44" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I44" s="62" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J44" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="58" customHeight="1">
-      <x:c r="A45" s="53" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B45" s="47" t="str">
-        <x:v>Case_A14_009</x:v>
-      </x:c>
-      <x:c r="C45" s="62" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="D45" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
-      </x:c>
-      <x:c r="E45" s="47" t="str">
-        <x:v>INVALID_ACTION；move failed</x:v>
-      </x:c>
-      <x:c r="F45" s="47" t="str">
-        <x:v>测试步骤未处理落点提示</x:v>
-      </x:c>
-      <x:c r="G45" s="47" t="str">
-        <x:v>Q从位置4 STEP 2后停在位置6的无主地产，会进入BUY提示；用例未先ANSWER就继续执行第二个STEP，因此在PROMPT阶段返回 move failed。</x:v>
-      </x:c>
-      <x:c r="H45" s="47" t="str">
-        <x:v>测试资产</x:v>
-      </x:c>
-      <x:c r="I45" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J45" s="47" t="str">
-        <x:v>保持业务期望不变，在两次移动之间补充拒绝购买的ANSWER，或调整首位玩家的终点使其不产生提示。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="58" customHeight="1">
-      <x:c r="A46" s="53" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B46" s="47" t="str">
-        <x:v>Case_A14_010</x:v>
-      </x:c>
-      <x:c r="C46" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D46" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
-      </x:c>
-      <x:c r="E46" s="47" t="str">
         <x:v>ASSERT_NOT_EQUAL；字段=actual.fortune；field missing in actual；期望={"position":null}；实际=null
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=1000；实际=900
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0
 ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=1000；实际=1100</x:v>
       </x:c>
+      <x:c r="F41" s="47" t="str">
+        <x:v>财神领取与免租未接入</x:v>
+      </x:c>
+      <x:c r="G41" s="47" t="str">
+        <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
+      </x:c>
+      <x:c r="H41" s="47" t="str">
+        <x:v>开发逻辑/测试接口</x:v>
+      </x:c>
+      <x:c r="I41" s="62" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J41" s="47" t="str">
+        <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="58" customHeight="1">
+      <x:c r="A42" s="53" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B42" s="47" t="str">
+        <x:v>Case_A14_011</x:v>
+      </x:c>
+      <x:c r="C42" s="62" t="str">
+        <x:v>ERROR</x:v>
+      </x:c>
+      <x:c r="D42" s="47" t="str">
+        <x:v>A14 财神随机出现与获取</x:v>
+      </x:c>
+      <x:c r="E42" s="47" t="str">
+        <x:v>INVALID_ACTION；unknown command</x:v>
+      </x:c>
+      <x:c r="F42" s="47" t="str">
+        <x:v>ADVANCE_TURN未实现</x:v>
+      </x:c>
+      <x:c r="G42" s="47" t="str">
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
+      </x:c>
+      <x:c r="H42" s="47" t="str">
+        <x:v>开发/测试接口适配</x:v>
+      </x:c>
+      <x:c r="I42" s="62" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J42" s="47" t="str">
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="58" customHeight="1">
+      <x:c r="A43" s="53" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B43" s="47" t="str">
+        <x:v>Case_A14_012</x:v>
+      </x:c>
+      <x:c r="C43" s="62" t="str">
+        <x:v>ERROR</x:v>
+      </x:c>
+      <x:c r="D43" s="47" t="str">
+        <x:v>A14 财神随机出现与获取</x:v>
+      </x:c>
+      <x:c r="E43" s="47" t="str">
+        <x:v>INVALID_ACTION；unknown command</x:v>
+      </x:c>
+      <x:c r="F43" s="47" t="str">
+        <x:v>ADVANCE_TURN未实现</x:v>
+      </x:c>
+      <x:c r="G43" s="47" t="str">
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
+      </x:c>
+      <x:c r="H43" s="47" t="str">
+        <x:v>开发/测试接口适配</x:v>
+      </x:c>
+      <x:c r="I43" s="62" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J43" s="47" t="str">
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="58" customHeight="1">
+      <x:c r="A44" s="53" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B44" s="47" t="str">
+        <x:v>Case_A15_003</x:v>
+      </x:c>
+      <x:c r="C44" s="62" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="D44" s="47" t="str">
+        <x:v>A15 礼品屋</x:v>
+      </x:c>
+      <x:c r="E44" s="47" t="str">
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0</x:v>
+      </x:c>
+      <x:c r="F44" s="47" t="str">
+        <x:v>礼品屋财神奖励未实现</x:v>
+      </x:c>
+      <x:c r="G44" s="47" t="str">
+        <x:v>选择礼品3后 god_of_wealth_rounds 仍为0，未获得预期的5回合财神状态；移动和提示回答本身已执行。</x:v>
+      </x:c>
+      <x:c r="H44" s="47" t="str">
+        <x:v>开发逻辑</x:v>
+      </x:c>
+      <x:c r="I44" s="62" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="J44" s="47" t="str">
+        <x:v>核对礼品编号3的定义并实现财神奖励；获得后立即将god_of_wealth_rounds设为5。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="58" customHeight="1">
+      <x:c r="A45" s="53" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B45" s="47" t="str">
+        <x:v>Case_A16_001</x:v>
+      </x:c>
+      <x:c r="C45" s="62" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="D45" s="47" t="str">
+        <x:v>A16 公园</x:v>
+      </x:c>
+      <x:c r="E45" s="47" t="str">
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+      </x:c>
+      <x:c r="F45" s="47" t="str">
+        <x:v>Actual缺少display_cells</x:v>
+      </x:c>
+      <x:c r="G45" s="47" t="str">
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+      </x:c>
+      <x:c r="H45" s="47" t="str">
+        <x:v>开发/测试接口适配</x:v>
+      </x:c>
+      <x:c r="I45" s="62" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="J45" s="47" t="str">
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="58" customHeight="1">
+      <x:c r="A46" s="53" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B46" s="47" t="str">
+        <x:v>Case_A16_002</x:v>
+      </x:c>
+      <x:c r="C46" s="62" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="D46" s="47" t="str">
+        <x:v>A16 公园</x:v>
+      </x:c>
+      <x:c r="E46" s="47" t="str">
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":49,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+      </x:c>
       <x:c r="F46" s="47" t="str">
-        <x:v>财神领取与免租未接入</x:v>
+        <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="G46" s="47" t="str">
-        <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
       </x:c>
       <x:c r="H46" s="47" t="str">
-        <x:v>开发逻辑/测试接口</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I46" s="62" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="J46" s="47" t="str">
-        <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
@@ -2517,31 +2470,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B47" s="47" t="str">
-        <x:v>Case_A14_011</x:v>
+        <x:v>Case_A16_003</x:v>
       </x:c>
       <x:c r="C47" s="62" t="str">
-        <x:v>ERROR</x:v>
+        <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D47" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
+        <x:v>A16 公园</x:v>
       </x:c>
       <x:c r="E47" s="47" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":63,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
       </x:c>
       <x:c r="F47" s="47" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
+        <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="G47" s="47" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
       </x:c>
       <x:c r="H47" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I47" s="62" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="J47" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
@@ -2549,31 +2502,31 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B48" s="47" t="str">
-        <x:v>Case_A14_012</x:v>
+        <x:v>Case_A16_007</x:v>
       </x:c>
       <x:c r="C48" s="62" t="str">
-        <x:v>ERROR</x:v>
+        <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D48" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
+        <x:v>A16 公园</x:v>
       </x:c>
       <x:c r="E48" s="47" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
       </x:c>
       <x:c r="F48" s="47" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
+        <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="G48" s="47" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
       </x:c>
       <x:c r="H48" s="47" t="str">
         <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I48" s="62" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="J48" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
@@ -2581,31 +2534,32 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B49" s="47" t="str">
-        <x:v>Case_A15_003</x:v>
+        <x:v>Case_A18_005</x:v>
       </x:c>
       <x:c r="C49" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D49" s="47" t="str">
-        <x:v>A15 礼品屋</x:v>
+        <x:v>A18 Step遥控骰子</x:v>
       </x:c>
       <x:c r="E49" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
+ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
       </x:c>
       <x:c r="F49" s="47" t="str">
-        <x:v>礼品屋财神奖励未实现</x:v>
+        <x:v>道具屋落点未触发PROMPT</x:v>
       </x:c>
       <x:c r="G49" s="47" t="str">
-        <x:v>选择礼品3后 god_of_wealth_rounds 仍为0，未获得预期的5回合财神状态；移动和提示回答本身已执行。</x:v>
+        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
       </x:c>
       <x:c r="H49" s="47" t="str">
-        <x:v>开发逻辑</x:v>
+        <x:v>开发逻辑/地图事件接入</x:v>
       </x:c>
       <x:c r="I49" s="62" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="J49" s="47" t="str">
-        <x:v>核对礼品编号3的定义并实现财神奖励；获得后立即将god_of_wealth_rounds设为5。</x:v>
+        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
@@ -2613,31 +2567,32 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B50" s="47" t="str">
-        <x:v>Case_A16_001</x:v>
+        <x:v>Case_A18_027</x:v>
       </x:c>
       <x:c r="C50" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D50" s="47" t="str">
-        <x:v>A16 公园</x:v>
+        <x:v>A18 Step遥控骰子</x:v>
       </x:c>
       <x:c r="E50" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
+ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
       </x:c>
       <x:c r="F50" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
+        <x:v>道具屋落点未触发PROMPT</x:v>
       </x:c>
       <x:c r="G50" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
       </x:c>
       <x:c r="H50" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
+        <x:v>开发逻辑/地图事件接入</x:v>
       </x:c>
       <x:c r="I50" s="62" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="J50" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
@@ -2645,228 +2600,66 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B51" s="47" t="str">
-        <x:v>Case_A16_002</x:v>
+        <x:v>Case_A21_028</x:v>
       </x:c>
       <x:c r="C51" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D51" s="47" t="str">
-        <x:v>A16 公园</x:v>
+        <x:v>A21 资金低于零破产</x:v>
       </x:c>
       <x:c r="E51" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":49,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
-      </x:c>
-      <x:c r="F51" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
-      </x:c>
-      <x:c r="G51" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
-      </x:c>
-      <x:c r="H51" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I51" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J51" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="58" customHeight="1">
-      <x:c r="A52" s="53" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B52" s="47" t="str">
-        <x:v>Case_A16_003</x:v>
-      </x:c>
-      <x:c r="C52" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D52" s="47" t="str">
-        <x:v>A16 公园</x:v>
-      </x:c>
-      <x:c r="E52" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":63,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
-      </x:c>
-      <x:c r="F52" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
-      </x:c>
-      <x:c r="G52" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
-      </x:c>
-      <x:c r="H52" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I52" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J52" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="58" customHeight="1">
-      <x:c r="A53" s="53" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B53" s="47" t="str">
-        <x:v>Case_A16_007</x:v>
-      </x:c>
-      <x:c r="C53" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D53" s="47" t="str">
-        <x:v>A16 公园</x:v>
-      </x:c>
-      <x:c r="E53" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
-      </x:c>
-      <x:c r="F53" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
-      </x:c>
-      <x:c r="G53" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
-      </x:c>
-      <x:c r="H53" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I53" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J53" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="58" customHeight="1">
-      <x:c r="A54" s="53" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B54" s="47" t="str">
-        <x:v>Case_A18_005</x:v>
-      </x:c>
-      <x:c r="C54" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D54" s="47" t="str">
-        <x:v>A18 Step遥控骰子</x:v>
-      </x:c>
-      <x:c r="E54" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
-ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
-      </x:c>
-      <x:c r="F54" s="47" t="str">
-        <x:v>道具屋落点未触发PROMPT</x:v>
-      </x:c>
-      <x:c r="G54" s="47" t="str">
-        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
-      </x:c>
-      <x:c r="H54" s="47" t="str">
-        <x:v>开发逻辑/地图事件接入</x:v>
-      </x:c>
-      <x:c r="I54" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J54" s="47" t="str">
-        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="58" customHeight="1">
-      <x:c r="A55" s="53" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B55" s="47" t="str">
-        <x:v>Case_A18_027</x:v>
-      </x:c>
-      <x:c r="C55" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D55" s="47" t="str">
-        <x:v>A18 Step遥控骰子</x:v>
-      </x:c>
-      <x:c r="E55" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
-ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
-      </x:c>
-      <x:c r="F55" s="47" t="str">
-        <x:v>道具屋落点未触发PROMPT</x:v>
-      </x:c>
-      <x:c r="G55" s="47" t="str">
-        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
-      </x:c>
-      <x:c r="H55" s="47" t="str">
-        <x:v>开发逻辑/地图事件接入</x:v>
-      </x:c>
-      <x:c r="I55" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J55" s="47" t="str">
-        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="58" customHeight="1">
-      <x:c r="A56" s="53" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B56" s="47" t="str">
-        <x:v>Case_A21_028</x:v>
-      </x:c>
-      <x:c r="C56" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D56" s="47" t="str">
-        <x:v>A21 资金低于零破产</x:v>
-      </x:c>
-      <x:c r="E56" s="47" t="str">
         <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=100；实际=-100
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].status；scalar not equal；期望="NORMAL"；实际="BANKRUPT"
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0
 ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=1000；实际=1100
 ASSERT_NOT_EQUAL；字段=actual.fortune；field missing in actual；期望={"position":null}；实际=null</x:v>
       </x:c>
-      <x:c r="F56" s="47" t="str">
+      <x:c r="F51" s="47" t="str">
         <x:v>财神领取与免租未接入</x:v>
       </x:c>
-      <x:c r="G56" s="47" t="str">
+      <x:c r="G51" s="47" t="str">
         <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
       </x:c>
-      <x:c r="H56" s="47" t="str">
+      <x:c r="H51" s="47" t="str">
         <x:v>开发逻辑/测试接口</x:v>
       </x:c>
-      <x:c r="I56" s="62" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J56" s="47" t="str">
+      <x:c r="I51" s="62" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J51" s="47" t="str">
         <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="58" customHeight="1">
-      <x:c r="A57" s="54" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B57" s="48" t="str">
+    <x:row r="52" ht="58" customHeight="1">
+      <x:c r="A52" s="54" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B52" s="48" t="str">
         <x:v>Case_A21_031</x:v>
       </x:c>
-      <x:c r="C57" s="63" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="D57" s="48" t="str">
+      <x:c r="C52" s="63" t="str">
+        <x:v>ERROR</x:v>
+      </x:c>
+      <x:c r="D52" s="48" t="str">
         <x:v>A21 资金低于零破产</x:v>
       </x:c>
-      <x:c r="E57" s="48" t="str">
+      <x:c r="E52" s="48" t="str">
         <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
-      <x:c r="F57" s="48" t="str">
+      <x:c r="F52" s="48" t="str">
         <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
-      <x:c r="G57" s="48" t="str">
+      <x:c r="G52" s="48" t="str">
         <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
-      <x:c r="H57" s="48" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I57" s="63" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J57" s="48" t="str">
+      <x:c r="H52" s="48" t="str">
+        <x:v>开发/测试接口适配</x:v>
+      </x:c>
+      <x:c r="I52" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J52" s="48" t="str">
         <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
@@ -2875,16 +2668,16 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C5:C57">
+  <x:conditionalFormatting sqref="C5:C52">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="ERROR"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="FAIL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I57">
+  <x:conditionalFormatting sqref="I5:I52">
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="P0"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reda14a3aa2f64f84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37d9a532999744ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2921,7 +2714,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>共35条；“责任归属”是基于当前报告和2.0规范的测试侧初步判断，修复后应重新执行一键回归确认。</x:v>
+        <x:v>共34条；“责任归属”是基于当前报告和2.0规范的测试侧初步判断，修复后应重新执行一键回归确认。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -3962,7 +3755,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="47" t="str">
-        <x:v>Case_A14_009</x:v>
+        <x:v>Case_A14_011</x:v>
       </x:c>
       <x:c r="C36" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -3971,22 +3764,22 @@
         <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E36" s="47" t="str">
-        <x:v>INVALID_ACTION；move failed</x:v>
+        <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
       <x:c r="F36" s="47" t="str">
-        <x:v>测试步骤未处理落点提示</x:v>
+        <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
       <x:c r="G36" s="47" t="str">
-        <x:v>Q从位置4 STEP 2后停在位置6的无主地产，会进入BUY提示；用例未先ANSWER就继续执行第二个STEP，因此在PROMPT阶段返回 move failed。</x:v>
+        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
       <x:c r="H36" s="47" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I36" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J36" s="47" t="str">
-        <x:v>保持业务期望不变，在两次移动之间补充拒绝购买的ANSWER，或调整首位玩家的终点使其不产生提示。</x:v>
+        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
@@ -3994,7 +3787,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" s="47" t="str">
-        <x:v>Case_A14_011</x:v>
+        <x:v>Case_A14_012</x:v>
       </x:c>
       <x:c r="C37" s="62" t="str">
         <x:v>ERROR</x:v>
@@ -4022,66 +3815,34 @@
       </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
-      <x:c r="A38" s="53" t="n">
+      <x:c r="A38" s="54" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B38" s="47" t="str">
-        <x:v>Case_A14_012</x:v>
-      </x:c>
-      <x:c r="C38" s="62" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="D38" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
-      </x:c>
-      <x:c r="E38" s="47" t="str">
+      <x:c r="B38" s="48" t="str">
+        <x:v>Case_A21_031</x:v>
+      </x:c>
+      <x:c r="C38" s="63" t="str">
+        <x:v>ERROR</x:v>
+      </x:c>
+      <x:c r="D38" s="48" t="str">
+        <x:v>A21 资金低于零破产</x:v>
+      </x:c>
+      <x:c r="E38" s="48" t="str">
         <x:v>INVALID_ACTION；unknown command</x:v>
       </x:c>
-      <x:c r="F38" s="47" t="str">
+      <x:c r="F38" s="48" t="str">
         <x:v>ADVANCE_TURN未实现</x:v>
       </x:c>
-      <x:c r="G38" s="47" t="str">
+      <x:c r="G38" s="48" t="str">
         <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
       </x:c>
-      <x:c r="H38" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I38" s="62" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J38" s="47" t="str">
-        <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="58" customHeight="1">
-      <x:c r="A39" s="54" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B39" s="48" t="str">
-        <x:v>Case_A21_031</x:v>
-      </x:c>
-      <x:c r="C39" s="63" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="D39" s="48" t="str">
-        <x:v>A21 资金低于零破产</x:v>
-      </x:c>
-      <x:c r="E39" s="48" t="str">
-        <x:v>INVALID_ACTION；unknown command</x:v>
-      </x:c>
-      <x:c r="F39" s="48" t="str">
-        <x:v>ADVANCE_TURN未实现</x:v>
-      </x:c>
-      <x:c r="G39" s="48" t="str">
-        <x:v>JSON 2.0规定 ADVANCE_TURN 为STATE测试专用控制动作，但当前 monopoly_test 将其识别为 unknown command，导致财神计时和回合推进场景无法执行。</x:v>
-      </x:c>
-      <x:c r="H39" s="48" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I39" s="63" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J39" s="48" t="str">
+      <x:c r="H38" s="48" t="str">
+        <x:v>开发/测试接口适配</x:v>
+      </x:c>
+      <x:c r="I38" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J38" s="48" t="str">
         <x:v>在STATE动作分发器实现 ADVANCE_TURN：原地结束当前玩家回合、切换玩家并推进回合/财神计时，不触发移动或落点事件。</x:v>
       </x:c>
     </x:row>
@@ -4090,16 +3851,16 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C5:C39">
+  <x:conditionalFormatting sqref="C5:C38">
     <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="ERROR"/>
     <x:cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="FAIL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I39">
+  <x:conditionalFormatting sqref="I5:I38">
     <x:cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="P0"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b1b76a4125b4b60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R245f8c3161e641b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4136,7 +3897,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>共18条；“责任归属”是基于当前报告和2.0规范的测试侧初步判断，修复后应重新执行一键回归确认。</x:v>
+        <x:v>共14条；“责任归属”是基于当前报告和2.0规范的测试侧初步判断，修复后应重新执行一键回归确认。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -4185,31 +3946,31 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="46" t="str">
-        <x:v>Case_A4_001</x:v>
+        <x:v>Case_A5_002</x:v>
       </x:c>
       <x:c r="C5" s="61" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D5" s="46" t="str">
-        <x:v>A4 回合控制与落点处理</x:v>
+        <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E5" s="46" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.current_user；scalar not equal；期望="A"；实际="Q"</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"2","visible_entity":"BASE"}]；实际=null</x:v>
       </x:c>
       <x:c r="F5" s="46" t="str">
-        <x:v>测试步骤未处理落点提示</x:v>
+        <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="G5" s="46" t="str">
-        <x:v>Q从公园49 STEP 1后到达位置50的无主地产，当前回合停留在BUY提示，故current_user仍为Q；用例却直接期望切换到A。</x:v>
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
       </x:c>
       <x:c r="H5" s="46" t="str">
-        <x:v>测试资产</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I5" s="61" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="J5" s="46" t="str">
-        <x:v>在STEP后补充ANSWER拒绝/购买，再断言切换到A；不能仅修改current_user期望来强行通过。</x:v>
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
@@ -4217,7 +3978,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="47" t="str">
-        <x:v>Case_A5_002</x:v>
+        <x:v>Case_A5_003</x:v>
       </x:c>
       <x:c r="C6" s="62" t="str">
         <x:v>FAIL</x:v>
@@ -4226,7 +3987,7 @@
         <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E6" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"2","visible_entity":"BASE"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"0","visible_entity":"BASE"}]；实际=null</x:v>
       </x:c>
       <x:c r="F6" s="47" t="str">
         <x:v>Actual缺少display_cells</x:v>
@@ -4249,7 +4010,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="47" t="str">
-        <x:v>Case_A5_003</x:v>
+        <x:v>Case_A5_004</x:v>
       </x:c>
       <x:c r="C7" s="62" t="str">
         <x:v>FAIL</x:v>
@@ -4258,7 +4019,7 @@
         <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E7" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"base_symbol":"0","visible_entity":"BASE"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":30,"visible_symbol":"#","visible_entity":"MAP_ITEM"}]；实际=null</x:v>
       </x:c>
       <x:c r="F7" s="47" t="str">
         <x:v>Actual缺少display_cells</x:v>
@@ -4281,7 +4042,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="47" t="str">
-        <x:v>Case_A5_004</x:v>
+        <x:v>Case_A5_005</x:v>
       </x:c>
       <x:c r="C8" s="62" t="str">
         <x:v>FAIL</x:v>
@@ -4290,7 +4051,7 @@
         <x:v>A5 地图显示</x:v>
       </x:c>
       <x:c r="E8" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":30,"visible_symbol":"#","visible_entity":"MAP_ITEM"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"visible_symbol":"Q","visible_entity":"PLAYER"}]；实际=null</x:v>
       </x:c>
       <x:c r="F8" s="47" t="str">
         <x:v>Actual缺少display_cells</x:v>
@@ -4313,31 +4074,32 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="47" t="str">
-        <x:v>Case_A5_005</x:v>
+        <x:v>Case_A14_009</x:v>
       </x:c>
       <x:c r="C9" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D9" s="47" t="str">
-        <x:v>A5 地图显示</x:v>
+        <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E9" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":10,"visible_symbol":"Q","visible_entity":"PLAYER"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.fortune；field missing in actual；期望={"position":null}；实际=null
+ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0</x:v>
       </x:c>
       <x:c r="F9" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
+        <x:v>财神领取与免租未接入</x:v>
       </x:c>
       <x:c r="G9" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+        <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
       </x:c>
       <x:c r="H9" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
+        <x:v>开发逻辑/测试接口</x:v>
       </x:c>
       <x:c r="I9" s="62" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="J9" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+        <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
@@ -4345,166 +4107,162 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="47" t="str">
-        <x:v>Case_A10_014</x:v>
+        <x:v>Case_A14_010</x:v>
       </x:c>
       <x:c r="C10" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D10" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
+        <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
       <x:c r="E10" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=5000；实际=4000
-ASSERT_NOT_EQUAL；字段=actual.players[id=S].fund；scalar not equal；期望=5000；实际=6000</x:v>
-      </x:c>
-      <x:c r="F10" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
-      </x:c>
-      <x:c r="G10" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
-      </x:c>
-      <x:c r="H10" s="47" t="str">
-        <x:v>测试资产</x:v>
-      </x:c>
-      <x:c r="I10" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J10" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="53" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B11" s="47" t="str">
-        <x:v>Case_A10_015</x:v>
-      </x:c>
-      <x:c r="C11" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D11" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
-      </x:c>
-      <x:c r="E11" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=S].fund；scalar not equal；期望=5000；实际=4700
-ASSERT_NOT_EQUAL；字段=actual.players[id=J].fund；scalar not equal；期望=5000；实际=5300</x:v>
-      </x:c>
-      <x:c r="F11" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
-      </x:c>
-      <x:c r="G11" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
-      </x:c>
-      <x:c r="H11" s="47" t="str">
-        <x:v>测试资产</x:v>
-      </x:c>
-      <x:c r="I11" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J11" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="58" customHeight="1">
-      <x:c r="A12" s="53" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="47" t="str">
-        <x:v>Case_A10_017</x:v>
-      </x:c>
-      <x:c r="C12" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D12" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
-      </x:c>
-      <x:c r="E12" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=5000；实际=4250
-ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=5000；实际=5750</x:v>
-      </x:c>
-      <x:c r="F12" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
-      </x:c>
-      <x:c r="G12" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
-      </x:c>
-      <x:c r="H12" s="47" t="str">
-        <x:v>测试资产</x:v>
-      </x:c>
-      <x:c r="I12" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J12" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="58" customHeight="1">
-      <x:c r="A13" s="53" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B13" s="47" t="str">
-        <x:v>Case_A10_018</x:v>
-      </x:c>
-      <x:c r="C13" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D13" s="47" t="str">
-        <x:v>A10 收取过路费</x:v>
-      </x:c>
-      <x:c r="E13" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=J].fund；scalar not equal；期望=5000；实际=4400
-ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=5000；实际=5600</x:v>
-      </x:c>
-      <x:c r="F13" s="47" t="str">
-        <x:v>JSON期望值转换错误</x:v>
-      </x:c>
-      <x:c r="G13" s="47" t="str">
-        <x:v>原Excel/source_trace明确要求支付对应过路费，实际资金变化也符合该本意；但活动JSON的expected仍把双方资金写成移动前数值5000，语义在转换时被压平。</x:v>
-      </x:c>
-      <x:c r="H13" s="47" t="str">
-        <x:v>测试资产</x:v>
-      </x:c>
-      <x:c r="I13" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J13" s="47" t="str">
-        <x:v>按原Excel本意修复JSON expected资金：A10_014=4000/6000，A10_015=4700/5300，A10_017=4250/5750，A10_018=4400/5600。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="58" customHeight="1">
-      <x:c r="A14" s="53" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B14" s="47" t="str">
-        <x:v>Case_A14_010</x:v>
-      </x:c>
-      <x:c r="C14" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D14" s="47" t="str">
-        <x:v>A14 财神随机出现与获取</x:v>
-      </x:c>
-      <x:c r="E14" s="47" t="str">
         <x:v>ASSERT_NOT_EQUAL；字段=actual.fortune；field missing in actual；期望={"position":null}；实际=null
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=1000；实际=900
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0
 ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=1000；实际=1100</x:v>
       </x:c>
+      <x:c r="F10" s="47" t="str">
+        <x:v>财神领取与免租未接入</x:v>
+      </x:c>
+      <x:c r="G10" s="47" t="str">
+        <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
+      </x:c>
+      <x:c r="H10" s="47" t="str">
+        <x:v>开发逻辑/测试接口</x:v>
+      </x:c>
+      <x:c r="I10" s="62" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J10" s="47" t="str">
+        <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="53" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="47" t="str">
+        <x:v>Case_A15_003</x:v>
+      </x:c>
+      <x:c r="C11" s="62" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="D11" s="47" t="str">
+        <x:v>A15 礼品屋</x:v>
+      </x:c>
+      <x:c r="E11" s="47" t="str">
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0</x:v>
+      </x:c>
+      <x:c r="F11" s="47" t="str">
+        <x:v>礼品屋财神奖励未实现</x:v>
+      </x:c>
+      <x:c r="G11" s="47" t="str">
+        <x:v>选择礼品3后 god_of_wealth_rounds 仍为0，未获得预期的5回合财神状态；移动和提示回答本身已执行。</x:v>
+      </x:c>
+      <x:c r="H11" s="47" t="str">
+        <x:v>开发逻辑</x:v>
+      </x:c>
+      <x:c r="I11" s="62" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="J11" s="47" t="str">
+        <x:v>核对礼品编号3的定义并实现财神奖励；获得后立即将god_of_wealth_rounds设为5。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="53" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="47" t="str">
+        <x:v>Case_A16_001</x:v>
+      </x:c>
+      <x:c r="C12" s="62" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="D12" s="47" t="str">
+        <x:v>A16 公园</x:v>
+      </x:c>
+      <x:c r="E12" s="47" t="str">
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+      </x:c>
+      <x:c r="F12" s="47" t="str">
+        <x:v>Actual缺少display_cells</x:v>
+      </x:c>
+      <x:c r="G12" s="47" t="str">
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+      </x:c>
+      <x:c r="H12" s="47" t="str">
+        <x:v>开发/测试接口适配</x:v>
+      </x:c>
+      <x:c r="I12" s="62" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="J12" s="47" t="str">
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="58" customHeight="1">
+      <x:c r="A13" s="53" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B13" s="47" t="str">
+        <x:v>Case_A16_002</x:v>
+      </x:c>
+      <x:c r="C13" s="62" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="D13" s="47" t="str">
+        <x:v>A16 公园</x:v>
+      </x:c>
+      <x:c r="E13" s="47" t="str">
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":49,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+      </x:c>
+      <x:c r="F13" s="47" t="str">
+        <x:v>Actual缺少display_cells</x:v>
+      </x:c>
+      <x:c r="G13" s="47" t="str">
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+      </x:c>
+      <x:c r="H13" s="47" t="str">
+        <x:v>开发/测试接口适配</x:v>
+      </x:c>
+      <x:c r="I13" s="62" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="J13" s="47" t="str">
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="58" customHeight="1">
+      <x:c r="A14" s="53" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" s="47" t="str">
+        <x:v>Case_A16_003</x:v>
+      </x:c>
+      <x:c r="C14" s="62" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="D14" s="47" t="str">
+        <x:v>A16 公园</x:v>
+      </x:c>
+      <x:c r="E14" s="47" t="str">
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":63,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+      </x:c>
       <x:c r="F14" s="47" t="str">
-        <x:v>财神领取与免租未接入</x:v>
+        <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="G14" s="47" t="str">
-        <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
       </x:c>
       <x:c r="H14" s="47" t="str">
-        <x:v>开发逻辑/测试接口</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I14" s="62" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="J14" s="47" t="str">
-        <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
@@ -4512,31 +4270,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="47" t="str">
-        <x:v>Case_A15_003</x:v>
+        <x:v>Case_A16_007</x:v>
       </x:c>
       <x:c r="C15" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D15" s="47" t="str">
-        <x:v>A15 礼品屋</x:v>
+        <x:v>A16 公园</x:v>
       </x:c>
       <x:c r="E15" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
       </x:c>
       <x:c r="F15" s="47" t="str">
-        <x:v>礼品屋财神奖励未实现</x:v>
+        <x:v>Actual缺少display_cells</x:v>
       </x:c>
       <x:c r="G15" s="47" t="str">
-        <x:v>选择礼品3后 god_of_wealth_rounds 仍为0，未获得预期的5回合财神状态；移动和提示回答本身已执行。</x:v>
+        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
       </x:c>
       <x:c r="H15" s="47" t="str">
-        <x:v>开发逻辑</x:v>
+        <x:v>开发/测试接口适配</x:v>
       </x:c>
       <x:c r="I15" s="62" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="J15" s="47" t="str">
-        <x:v>核对礼品编号3的定义并实现财神奖励；获得后立即将god_of_wealth_rounds设为5。</x:v>
+        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -4544,31 +4302,32 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="47" t="str">
-        <x:v>Case_A16_001</x:v>
+        <x:v>Case_A18_005</x:v>
       </x:c>
       <x:c r="C16" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D16" s="47" t="str">
-        <x:v>A16 公园</x:v>
+        <x:v>A18 Step遥控骰子</x:v>
       </x:c>
       <x:c r="E16" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
+ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
       </x:c>
       <x:c r="F16" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
+        <x:v>道具屋落点未触发PROMPT</x:v>
       </x:c>
       <x:c r="G16" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
       </x:c>
       <x:c r="H16" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
+        <x:v>开发逻辑/地图事件接入</x:v>
       </x:c>
       <x:c r="I16" s="62" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="J16" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
@@ -4576,196 +4335,67 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="47" t="str">
-        <x:v>Case_A16_002</x:v>
+        <x:v>Case_A18_027</x:v>
       </x:c>
       <x:c r="C17" s="62" t="str">
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="D17" s="47" t="str">
-        <x:v>A16 公园</x:v>
+        <x:v>A18 Step遥控骰子</x:v>
       </x:c>
       <x:c r="E17" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":49,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
+        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
+ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
       </x:c>
       <x:c r="F17" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
+        <x:v>道具屋落点未触发PROMPT</x:v>
       </x:c>
       <x:c r="G17" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
+        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
       </x:c>
       <x:c r="H17" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
+        <x:v>开发逻辑/地图事件接入</x:v>
       </x:c>
       <x:c r="I17" s="62" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="J17" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
+        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
-      <x:c r="A18" s="53" t="n">
+      <x:c r="A18" s="54" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B18" s="47" t="str">
-        <x:v>Case_A16_003</x:v>
-      </x:c>
-      <x:c r="C18" s="62" t="str">
+      <x:c r="B18" s="48" t="str">
+        <x:v>Case_A21_028</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
         <x:v>FAIL</x:v>
       </x:c>
-      <x:c r="D18" s="47" t="str">
-        <x:v>A16 公园</x:v>
-      </x:c>
-      <x:c r="E18" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":63,"base_type":"PARK","base_symbol":"P","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
-      </x:c>
-      <x:c r="F18" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
-      </x:c>
-      <x:c r="G18" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
-      </x:c>
-      <x:c r="H18" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I18" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J18" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="58" customHeight="1">
-      <x:c r="A19" s="53" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B19" s="47" t="str">
-        <x:v>Case_A16_007</x:v>
-      </x:c>
-      <x:c r="C19" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D19" s="47" t="str">
-        <x:v>A16 公园</x:v>
-      </x:c>
-      <x:c r="E19" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.display_cells；field missing in actual；期望=[{"position":14,"base_type":"PARK","visible_symbol":"P","visible_entity":"BASE"}]；实际=null</x:v>
-      </x:c>
-      <x:c r="F19" s="47" t="str">
-        <x:v>Actual缺少display_cells</x:v>
-      </x:c>
-      <x:c r="G19" s="47" t="str">
-        <x:v>2.0规范要求STATE Actual输出display_cells以验证底层格、玩家、道具和财神的显示覆盖关系；当前实际结果完全缺少该字段。</x:v>
-      </x:c>
-      <x:c r="H19" s="47" t="str">
-        <x:v>开发/测试接口适配</x:v>
-      </x:c>
-      <x:c r="I19" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J19" s="47" t="str">
-        <x:v>在 monopoly_test 的Actual序列化中输出按position组织的display_cells，并实现base_symbol、visible_symbol、visible_entity等字段。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="58" customHeight="1">
-      <x:c r="A20" s="53" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B20" s="47" t="str">
-        <x:v>Case_A18_005</x:v>
-      </x:c>
-      <x:c r="C20" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D20" s="47" t="str">
-        <x:v>A18 Step遥控骰子</x:v>
-      </x:c>
-      <x:c r="E20" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
-ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
-      </x:c>
-      <x:c r="F20" s="47" t="str">
-        <x:v>道具屋落点未触发PROMPT</x:v>
-      </x:c>
-      <x:c r="G20" s="47" t="str">
-        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
-      </x:c>
-      <x:c r="H20" s="47" t="str">
-        <x:v>开发逻辑/地图事件接入</x:v>
-      </x:c>
-      <x:c r="I20" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J20" s="47" t="str">
-        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="58" customHeight="1">
-      <x:c r="A21" s="53" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B21" s="47" t="str">
-        <x:v>Case_A18_027</x:v>
-      </x:c>
-      <x:c r="C21" s="62" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D21" s="47" t="str">
-        <x:v>A18 Step遥控骰子</x:v>
-      </x:c>
-      <x:c r="E21" s="47" t="str">
-        <x:v>ASSERT_NOT_EQUAL；字段=actual.phase；scalar not equal；期望="PROMPT"；实际="COMMAND"
-ASSERT_NOT_EQUAL；字段=actual.pending_prompt；scalar not equal；期望="TOOL_SHOP"；实际=null</x:v>
-      </x:c>
-      <x:c r="F21" s="47" t="str">
-        <x:v>道具屋落点未触发PROMPT</x:v>
-      </x:c>
-      <x:c r="G21" s="47" t="str">
-        <x:v>玩家最终位置应为地图28（TOOL_SHOP），但Actual保持COMMAND且pending_prompt=null，说明落点事件没有进入TOOL_SHOP提示。</x:v>
-      </x:c>
-      <x:c r="H21" s="47" t="str">
-        <x:v>开发逻辑/地图事件接入</x:v>
-      </x:c>
-      <x:c r="I21" s="62" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="J21" s="47" t="str">
-        <x:v>核对位置28地图类型和STEP落点事件分发；到达道具屋时设置phase=PROMPT、pending_prompt=TOOL_SHOP。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="58" customHeight="1">
-      <x:c r="A22" s="54" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B22" s="48" t="str">
-        <x:v>Case_A21_028</x:v>
-      </x:c>
-      <x:c r="C22" s="63" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="D22" s="48" t="str">
+      <x:c r="D18" s="48" t="str">
         <x:v>A21 资金低于零破产</x:v>
       </x:c>
-      <x:c r="E22" s="48" t="str">
+      <x:c r="E18" s="48" t="str">
         <x:v>ASSERT_NOT_EQUAL；字段=actual.players[id=Q].fund；scalar not equal；期望=100；实际=-100
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].status；scalar not equal；期望="NORMAL"；实际="BANKRUPT"
 ASSERT_NOT_EQUAL；字段=actual.players[id=Q].god_of_wealth_rounds；scalar not equal；期望=5；实际=0
 ASSERT_NOT_EQUAL；字段=actual.players[id=A].fund；scalar not equal；期望=1000；实际=1100
 ASSERT_NOT_EQUAL；字段=actual.fortune；field missing in actual；期望={"position":null}；实际=null</x:v>
       </x:c>
-      <x:c r="F22" s="48" t="str">
+      <x:c r="F18" s="48" t="str">
         <x:v>财神领取与免租未接入</x:v>
       </x:c>
-      <x:c r="G22" s="48" t="str">
+      <x:c r="G18" s="48" t="str">
         <x:v>玩家经过预置F后，Actual没有fortune字段，god_of_wealth_rounds仍为0且照常扣租，说明财神领取、地图移除及当轮免租链路尚未实现或未接入STATE测试入口。</x:v>
       </x:c>
-      <x:c r="H22" s="48" t="str">
+      <x:c r="H18" s="48" t="str">
         <x:v>开发逻辑/测试接口</x:v>
       </x:c>
-      <x:c r="I22" s="63" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="J22" s="48" t="str">
+      <x:c r="I18" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="J18" s="48" t="str">
         <x:v>实现/接入经过F立即领取、状态设为5、F从地图消失，并在同一次移动的租金结算前生效。</x:v>
       </x:c>
     </x:row>
@@ -4774,16 +4404,16 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C5:C22">
+  <x:conditionalFormatting sqref="C5:C18">
     <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="ERROR"/>
     <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="FAIL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I5:I22">
+  <x:conditionalFormatting sqref="I5:I18">
     <x:cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="P0"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc130a2eaf6784074"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3013a9ca7b345f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>